--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>89.35855258676679</v>
+        <v>14.5207647953496</v>
       </c>
       <c r="D2" t="n">
-        <v>80.14067918608801</v>
+        <v>13.0228603677393</v>
       </c>
       <c r="E2" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F2" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.91303997261127</v>
+        <v>12.49836899554933</v>
       </c>
       <c r="D3" t="n">
-        <v>60.28274883991934</v>
+        <v>9.795946686486893</v>
       </c>
       <c r="E3" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F3" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.08527616438472</v>
+        <v>12.68885737671252</v>
       </c>
       <c r="D4" t="n">
-        <v>63.35331335506046</v>
+        <v>10.29491342019733</v>
       </c>
       <c r="E4" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F4" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>96.90643296729039</v>
+        <v>15.74729535718469</v>
       </c>
       <c r="D5" t="n">
-        <v>75.97876119927072</v>
+        <v>12.34654869488149</v>
       </c>
       <c r="E5" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F5" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>90.70384604127125</v>
+        <v>14.73937498170658</v>
       </c>
       <c r="D6" t="n">
-        <v>84.82305956581509</v>
+        <v>13.78374717944495</v>
       </c>
       <c r="E6" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F6" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>69.05654646806256</v>
+        <v>11.22168880106017</v>
       </c>
       <c r="D7" t="n">
-        <v>50.77521701879796</v>
+        <v>8.250972765554669</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F7" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>72.92544648409455</v>
+        <v>11.85038505366536</v>
       </c>
       <c r="D8" t="n">
-        <v>60.2693187222824</v>
+        <v>9.79376429237089</v>
       </c>
       <c r="E8" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F8" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>105.6445711949883</v>
+        <v>17.1672428191856</v>
       </c>
       <c r="D9" t="n">
-        <v>86.15140563154809</v>
+        <v>13.99960341512656</v>
       </c>
       <c r="E9" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F9" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.86379342861952</v>
+        <v>10.86536643215067</v>
       </c>
       <c r="D10" t="n">
-        <v>50.93409549207569</v>
+        <v>8.276790517462301</v>
       </c>
       <c r="E10" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F10" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>87.75920169849041</v>
+        <v>14.26087027600469</v>
       </c>
       <c r="D11" t="n">
-        <v>66.65310808703538</v>
+        <v>10.83113006414325</v>
       </c>
       <c r="E11" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F11" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>73.79686920284996</v>
+        <v>11.99199124546312</v>
       </c>
       <c r="D12" t="n">
-        <v>52.12119940280982</v>
+        <v>8.469694902956597</v>
       </c>
       <c r="E12" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F12" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.528822897235</v>
+        <v>10.81093372080069</v>
       </c>
       <c r="D13" t="n">
-        <v>44.80577469383522</v>
+        <v>7.280938387748223</v>
       </c>
       <c r="E13" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F13" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.05434552916826</v>
+        <v>9.758831148489842</v>
       </c>
       <c r="D14" t="n">
-        <v>46.24328604117294</v>
+        <v>7.514533981690603</v>
       </c>
       <c r="E14" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F14" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.44941991330104</v>
+        <v>9.98553073591142</v>
       </c>
       <c r="D15" t="n">
-        <v>40.18322415991205</v>
+        <v>6.529773925985708</v>
       </c>
       <c r="E15" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F15" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>103.9488776039401</v>
+        <v>16.89169261064026</v>
       </c>
       <c r="D16" t="n">
-        <v>85.95311131034572</v>
+        <v>13.96738058793118</v>
       </c>
       <c r="E16" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F16" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>59.29286749050505</v>
+        <v>9.635090967207072</v>
       </c>
       <c r="D17" t="n">
-        <v>48.7914021542279</v>
+        <v>7.928602850062035</v>
       </c>
       <c r="E17" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F17" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.32131122998484</v>
+        <v>8.664713074872536</v>
       </c>
       <c r="D18" t="n">
-        <v>36.33998166622223</v>
+        <v>5.905247020761112</v>
       </c>
       <c r="E18" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F18" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>79.25356356154776</v>
+        <v>12.87870407875151</v>
       </c>
       <c r="D19" t="n">
-        <v>74.54734573535501</v>
+        <v>12.11394368199519</v>
       </c>
       <c r="E19" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F19" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>99.76327218844634</v>
+        <v>16.21153173062253</v>
       </c>
       <c r="D20" t="n">
-        <v>82.83539324136123</v>
+        <v>13.4607514017212</v>
       </c>
       <c r="E20" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F20" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84.59769286608648</v>
+        <v>13.74712509073905</v>
       </c>
       <c r="D21" t="n">
-        <v>66.54819695813322</v>
+        <v>10.81408200569665</v>
       </c>
       <c r="E21" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F21" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>55.34152034121554</v>
+        <v>8.992997055447526</v>
       </c>
       <c r="D22" t="n">
-        <v>33.99546298972465</v>
+        <v>5.524262735830256</v>
       </c>
       <c r="E22" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F22" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>70.02489135092597</v>
+        <v>11.37904484452547</v>
       </c>
       <c r="D23" t="n">
-        <v>70.58008841372175</v>
+        <v>11.46926436722979</v>
       </c>
       <c r="E23" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F23" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>57.95204938655758</v>
+        <v>9.417208025315606</v>
       </c>
       <c r="D24" t="n">
-        <v>39.05233222797222</v>
+        <v>6.346003987045487</v>
       </c>
       <c r="E24" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F24" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>59.13322628727409</v>
+        <v>9.609149271682041</v>
       </c>
       <c r="D25" t="n">
-        <v>59.65820491165094</v>
+        <v>9.694458298143278</v>
       </c>
       <c r="E25" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F25" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>57.09049902868496</v>
+        <v>9.277206092161306</v>
       </c>
       <c r="D26" t="n">
-        <v>40.93181865759127</v>
+        <v>6.651420531858582</v>
       </c>
       <c r="E26" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F26" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>86.0654742950324</v>
+        <v>13.98563957294277</v>
       </c>
       <c r="D27" t="n">
-        <v>72.87794678141078</v>
+        <v>11.84266635197925</v>
       </c>
       <c r="E27" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F27" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>81.40546584629946</v>
+        <v>13.22838820002366</v>
       </c>
       <c r="D28" t="n">
-        <v>68.74627407749391</v>
+        <v>11.17126953759276</v>
       </c>
       <c r="E28" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F28" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>36.48346011846323</v>
+        <v>5.928562269250276</v>
       </c>
       <c r="D29" t="n">
-        <v>36.95444092757027</v>
+        <v>6.005096650730168</v>
       </c>
       <c r="E29" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F29" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>55.93994561966158</v>
+        <v>9.090241163195007</v>
       </c>
       <c r="D30" t="n">
-        <v>43.91043984150173</v>
+        <v>7.135446474244032</v>
       </c>
       <c r="E30" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F30" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>44.47223249243724</v>
+        <v>7.226737780021052</v>
       </c>
       <c r="D31" t="n">
-        <v>32.33604001891657</v>
+        <v>5.254606503073943</v>
       </c>
       <c r="E31" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F31" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>70.71857986015777</v>
+        <v>11.49176922727564</v>
       </c>
       <c r="D32" t="n">
-        <v>59.32933968420681</v>
+        <v>9.641017698683608</v>
       </c>
       <c r="E32" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F32" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>84.49971884774051</v>
+        <v>13.73120431275783</v>
       </c>
       <c r="D33" t="n">
-        <v>74.0827449416437</v>
+        <v>12.0384460530171</v>
       </c>
       <c r="E33" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F33" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>34.20086203914214</v>
+        <v>5.557640081360598</v>
       </c>
       <c r="D34" t="n">
-        <v>34.24337323118488</v>
+        <v>5.564548150067544</v>
       </c>
       <c r="E34" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F34" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>88.54150043155799</v>
+        <v>14.38799382012817</v>
       </c>
       <c r="D35" t="n">
-        <v>78.60711917533396</v>
+        <v>12.77365686599177</v>
       </c>
       <c r="E35" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F35" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>33.5043132217612</v>
+        <v>5.444450898536195</v>
       </c>
       <c r="D36" t="n">
-        <v>33.06768043026466</v>
+        <v>5.373498069918007</v>
       </c>
       <c r="E36" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F36" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>27.98671649730288</v>
+        <v>4.547841430811718</v>
       </c>
       <c r="D37" t="n">
-        <v>28.28324673957396</v>
+        <v>4.596027595180769</v>
       </c>
       <c r="E37" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F37" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>63.70603092176378</v>
+        <v>10.35223002478661</v>
       </c>
       <c r="D38" t="n">
-        <v>59.67609119317434</v>
+        <v>9.697364818890831</v>
       </c>
       <c r="E38" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F38" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>76.16234626352644</v>
+        <v>12.37638126782305</v>
       </c>
       <c r="D39" t="n">
-        <v>71.54875339641767</v>
+        <v>11.62667242691787</v>
       </c>
       <c r="E39" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F39" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>52.19105245319491</v>
+        <v>8.481046023644174</v>
       </c>
       <c r="D40" t="n">
-        <v>50.85315086758242</v>
+        <v>8.263637015982145</v>
       </c>
       <c r="E40" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F40" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>33.03272894126076</v>
+        <v>5.367818452954874</v>
       </c>
       <c r="D41" t="n">
-        <v>31.66265377950269</v>
+        <v>5.145181239169187</v>
       </c>
       <c r="E41" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F41" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>40.18306147963656</v>
+        <v>6.529747490440941</v>
       </c>
       <c r="D42" t="n">
-        <v>40.27036414920798</v>
+        <v>6.543934174246297</v>
       </c>
       <c r="E42" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F42" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>67.79968242977588</v>
+        <v>11.01744839483858</v>
       </c>
       <c r="D43" t="n">
-        <v>66.24309277904756</v>
+        <v>10.76450257659523</v>
       </c>
       <c r="E43" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F43" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>52.62945876612453</v>
+        <v>8.552287049495236</v>
       </c>
       <c r="D44" t="n">
-        <v>51.209421226679</v>
+        <v>8.321530949335337</v>
       </c>
       <c r="E44" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F44" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>77.48704671129457</v>
+        <v>12.59164509058537</v>
       </c>
       <c r="D45" t="n">
-        <v>76.27791421214833</v>
+        <v>12.3951610594741</v>
       </c>
       <c r="E45" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F45" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>63.72066943081639</v>
+        <v>10.35460878250766</v>
       </c>
       <c r="D46" t="n">
-        <v>63.62240865432165</v>
+        <v>10.33864140632727</v>
       </c>
       <c r="E46" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F46" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>37.75769633105919</v>
+        <v>6.135625653797119</v>
       </c>
       <c r="D47" t="n">
-        <v>36.61121873856369</v>
+        <v>5.949323045016599</v>
       </c>
       <c r="E47" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F47" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>38.30945649807863</v>
+        <v>6.225286680937778</v>
       </c>
       <c r="D48" t="n">
-        <v>36.65934360959827</v>
+        <v>5.957143336559718</v>
       </c>
       <c r="E48" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F48" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>59.62828200623606</v>
+        <v>9.68959582601336</v>
       </c>
       <c r="D49" t="n">
-        <v>57.9812204887203</v>
+        <v>9.421948329417051</v>
       </c>
       <c r="E49" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F49" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>39.95503429386316</v>
+        <v>6.492693072752765</v>
       </c>
       <c r="D50" t="n">
-        <v>37.93046801067187</v>
+        <v>6.163701051734178</v>
       </c>
       <c r="E50" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F50" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>85.15395600831343</v>
+        <v>13.83751785135093</v>
       </c>
       <c r="D51" t="n">
-        <v>84.8375400432268</v>
+        <v>13.78610025702435</v>
       </c>
       <c r="E51" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F51" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>75.54921382191557</v>
+        <v>12.27674724606128</v>
       </c>
       <c r="D52" t="n">
-        <v>73.84988211856449</v>
+        <v>12.00060584426673</v>
       </c>
       <c r="E52" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F52" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>52.34116069646747</v>
+        <v>8.505438613175963</v>
       </c>
       <c r="D53" t="n">
-        <v>50.97400084126595</v>
+        <v>8.283275136705717</v>
       </c>
       <c r="E53" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F53" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>57.58705701150728</v>
+        <v>9.357896764369933</v>
       </c>
       <c r="D54" t="n">
-        <v>56.3629295048744</v>
+        <v>9.15897604454209</v>
       </c>
       <c r="E54" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F54" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>59.10106501366627</v>
+        <v>9.603923064720769</v>
       </c>
       <c r="D55" t="n">
-        <v>57.36582742107687</v>
+        <v>9.321946955924991</v>
       </c>
       <c r="E55" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F55" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>75.77038456745558</v>
+        <v>12.31268749221153</v>
       </c>
       <c r="D56" t="n">
-        <v>74.61090162002641</v>
+        <v>12.12427151325429</v>
       </c>
       <c r="E56" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F56" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>93.3982678590429</v>
+        <v>15.17721852709447</v>
       </c>
       <c r="D57" t="n">
-        <v>92.5549135342967</v>
+        <v>15.04017344932321</v>
       </c>
       <c r="E57" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F57" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>84.93456441772426</v>
+        <v>13.80186671788019</v>
       </c>
       <c r="D58" t="n">
-        <v>83.0107386305323</v>
+        <v>13.4892450274615</v>
       </c>
       <c r="E58" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F58" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>78.16947289772278</v>
+        <v>12.70253934587995</v>
       </c>
       <c r="D59" t="n">
-        <v>76.16919228762276</v>
+        <v>12.3774937467387</v>
       </c>
       <c r="E59" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F59" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>93.808957426226</v>
+        <v>15.24395558176173</v>
       </c>
       <c r="D60" t="n">
-        <v>92.82947206021103</v>
+        <v>15.08478920978429</v>
       </c>
       <c r="E60" t="n">
-        <v>19.35848995821202</v>
+        <v>3.145754618209454</v>
       </c>
       <c r="F60" t="n">
-        <v>17.90474070078604</v>
+        <v>2.909520363877731</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
